--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1572,13 +1572,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98EAA8CA-F47A-4310-9E85-CF09645EA0EF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38130EE6-7C12-419F-9F90-E2DD3D4CCC72}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62B50923-7751-4128-AD31-9C5A21D7C3CF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37DB5D02-7612-4D5A-81F0-8AFCC69C8878}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2AD8200-CDB4-4366-8C63-3E81125AF66C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E43C9845-3008-4D51-AB11-298DED3AA347}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1572,13 +1572,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38130EE6-7C12-419F-9F90-E2DD3D4CCC72}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7C4ECB4-6F43-4542-8920-1A704C518D88}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37DB5D02-7612-4D5A-81F0-8AFCC69C8878}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{608F7BCE-28F4-4FDF-AF43-A2B10290441B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E43C9845-3008-4D51-AB11-298DED3AA347}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7947FA5-32C5-4C12-AB65-0006A4937403}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1572,13 +1572,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7C4ECB4-6F43-4542-8920-1A704C518D88}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C42E30B-9167-4348-8B2C-CB23D6196AE0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{608F7BCE-28F4-4FDF-AF43-A2B10290441B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5839B40C-8211-4F2D-9944-65B132DD4B6C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7947FA5-32C5-4C12-AB65-0006A4937403}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02C7B269-1489-4924-9D26-0879C0F58779}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1563,22 +1563,22 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38130EE6-7C12-419F-9F90-E2DD3D4CCC72}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0F9F7E5-0ED3-4967-BF0A-ECEC2CF88FCD}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37DB5D02-7612-4D5A-81F0-8AFCC69C8878}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6008F81D-8B54-4A44-9A0B-7ADBAC936023}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E43C9845-3008-4D51-AB11-298DED3AA347}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53ED6323-82D3-4C5F-9C5C-DFE2AE39A553}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1563,22 +1563,22 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C42E30B-9167-4348-8B2C-CB23D6196AE0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB10B30A-E938-4075-8C11-59AF5BA522ED}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5839B40C-8211-4F2D-9944-65B132DD4B6C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{297AE21B-6015-446D-BC89-35DC57ED4EA7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02C7B269-1489-4924-9D26-0879C0F58779}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10565059-FB83-4542-91B4-64CE9596AAE6}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1572,13 +1572,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB10B30A-E938-4075-8C11-59AF5BA522ED}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47338396-EAA2-4EEE-9BAC-F5513804523E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{297AE21B-6015-446D-BC89-35DC57ED4EA7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E312C567-05CA-40E9-8147-669445E7940F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10565059-FB83-4542-91B4-64CE9596AAE6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C02830B-9B6A-4E4C-94C7-D31C60816667}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1572,13 +1572,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47338396-EAA2-4EEE-9BAC-F5513804523E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9658D6C2-7E53-41C0-BD22-F2C0ADEC35C0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E312C567-05CA-40E9-8147-669445E7940F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89C76CB1-84E6-4CA3-BC7A-F30FEFCA8A16}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C02830B-9B6A-4E4C-94C7-D31C60816667}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3814BB39-9DA3-4416-AC80-A0A50D5F072D}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1572,13 +1572,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9658D6C2-7E53-41C0-BD22-F2C0ADEC35C0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C404DD2E-789F-44D3-A784-D231D2330355}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89C76CB1-84E6-4CA3-BC7A-F30FEFCA8A16}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9DBB00A9-32FC-474F-A196-25B0BB61C704}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3814BB39-9DA3-4416-AC80-A0A50D5F072D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{439C566E-C285-4FF5-8FE8-88D6D15A9563}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1572,13 +1572,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C404DD2E-789F-44D3-A784-D231D2330355}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21CEB6BE-FA66-4D18-97D4-031669FE3DDC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9DBB00A9-32FC-474F-A196-25B0BB61C704}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83457039-9554-4794-9243-8E3CF9D3D301}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{439C566E-C285-4FF5-8FE8-88D6D15A9563}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8164A357-41A4-44F4-B9CC-7FDA8BCD0E01}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1572,13 +1572,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21CEB6BE-FA66-4D18-97D4-031669FE3DDC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{22BA0E28-9BA5-4E2B-A7C9-4267DFFE5FDA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83457039-9554-4794-9243-8E3CF9D3D301}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69FBD42C-8145-4E81-9EF0-676A8B4825F5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8164A357-41A4-44F4-B9CC-7FDA8BCD0E01}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{325B52D0-A517-499F-B48D-82C9FDD84477}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1572,13 +1572,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{22BA0E28-9BA5-4E2B-A7C9-4267DFFE5FDA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{266DD27A-1451-47BD-8BA7-0D5EF91E31C5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69FBD42C-8145-4E81-9EF0-676A8B4825F5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1870A7A8-48AC-4D94-8745-79CE6DF4B025}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{325B52D0-A517-499F-B48D-82C9FDD84477}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8DA7C9B-6AE4-4138-B973-50CE15F85070}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1572,13 +1572,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{266DD27A-1451-47BD-8BA7-0D5EF91E31C5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76A3D3DF-1357-449F-B532-1246152167B8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1870A7A8-48AC-4D94-8745-79CE6DF4B025}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1270172-E3CA-44A5-95F9-3EC913545942}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8DA7C9B-6AE4-4138-B973-50CE15F85070}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67FD1A5E-C302-4CA2-824D-ACBE2F0D5A68}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1572,13 +1572,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76A3D3DF-1357-449F-B532-1246152167B8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21902FDB-E471-4397-9141-83D9105DE546}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1270172-E3CA-44A5-95F9-3EC913545942}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{846A5332-4DD6-4FFF-8CAB-1A216E56D100}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67FD1A5E-C302-4CA2-824D-ACBE2F0D5A68}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{657451A2-E478-47B1-8971-A33422670132}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1572,13 +1572,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21902FDB-E471-4397-9141-83D9105DE546}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB39E8A9-8CA0-4E57-B09F-D2EF80988A84}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{846A5332-4DD6-4FFF-8CAB-1A216E56D100}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B520F045-689E-407D-9A35-07E5A6A49CF3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{657451A2-E478-47B1-8971-A33422670132}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE99ADE5-3619-4719-9188-C811B49E1FDF}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1572,13 +1572,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB39E8A9-8CA0-4E57-B09F-D2EF80988A84}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BEF9C873-9B11-48EE-9B7C-32CF2C4BE72A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B520F045-689E-407D-9A35-07E5A6A49CF3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D3550C0-FD5A-43AD-BBC1-B3B0D323B6F2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE99ADE5-3619-4719-9188-C811B49E1FDF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A98E8F50-3DF3-4690-ADD4-ACAC0107066B}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1572,13 +1572,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BEF9C873-9B11-48EE-9B7C-32CF2C4BE72A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76E50C3F-5B07-41D0-ACFE-BC9D46A69D48}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D3550C0-FD5A-43AD-BBC1-B3B0D323B6F2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F511AA8-95FF-4024-A6BC-98040759A6EF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A98E8F50-3DF3-4690-ADD4-ACAC0107066B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D56DF43C-8AB2-476F-AF2B-408AAFC1B278}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1572,13 +1572,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76E50C3F-5B07-41D0-ACFE-BC9D46A69D48}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A7263B7-1F5F-4DA6-A510-90BF81B8146D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F511AA8-95FF-4024-A6BC-98040759A6EF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2005F4AA-4D80-4AD2-A827-64CF4A8B6674}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D56DF43C-8AB2-476F-AF2B-408AAFC1B278}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7A35BF3F-8FFE-4DD5-A430-7BE4951F6982}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1572,13 +1572,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A7263B7-1F5F-4DA6-A510-90BF81B8146D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD3A52F2-A346-493E-9375-E472D7B71B73}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2005F4AA-4D80-4AD2-A827-64CF4A8B6674}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E154579D-96B0-4ADF-A53C-74ADD7C43ECF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7A35BF3F-8FFE-4DD5-A430-7BE4951F6982}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E71C04B3-2D42-4808-90B1-D5B4BF67686E}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1572,13 +1572,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD3A52F2-A346-493E-9375-E472D7B71B73}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71744533-FCB4-4876-B88D-9AA135478CE3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E154579D-96B0-4ADF-A53C-74ADD7C43ECF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1913DCAF-1936-49E9-B144-FD6C9D961443}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E71C04B3-2D42-4808-90B1-D5B4BF67686E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6C25767-9D9E-4282-862E-98E46219DC16}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1572,13 +1572,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71744533-FCB4-4876-B88D-9AA135478CE3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{722857B1-4EC5-49ED-9B22-570091954B28}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1913DCAF-1936-49E9-B144-FD6C9D961443}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D43F03D-3844-4CB7-91F7-2F6C948476BE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6C25767-9D9E-4282-862E-98E46219DC16}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D6D0324-76F2-4E61-B00D-101ED7328C32}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1572,13 +1572,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{722857B1-4EC5-49ED-9B22-570091954B28}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F01CFEC7-ED46-4ACC-8E6B-5A866BD0E80A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D43F03D-3844-4CB7-91F7-2F6C948476BE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D71F708-E2EB-4CE8-932C-3F8A6C6CFC6A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D6D0324-76F2-4E61-B00D-101ED7328C32}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0597F942-64EB-4B75-9D5C-5740AEB4BA5E}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1572,13 +1572,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F01CFEC7-ED46-4ACC-8E6B-5A866BD0E80A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D4CAE3C-03FB-4986-BE96-A5643188D2A3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D71F708-E2EB-4CE8-932C-3F8A6C6CFC6A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F3FA657-238A-46AF-A743-621036B4B389}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0597F942-64EB-4B75-9D5C-5740AEB4BA5E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D39B7D6A-118E-49A0-BE97-86074BAE05AD}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1572,13 +1572,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D4CAE3C-03FB-4986-BE96-A5643188D2A3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05B840FD-5718-4EFE-BE82-D414873726FE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F3FA657-238A-46AF-A743-621036B4B389}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58004295-57F5-43BD-9954-C99ADE0D3549}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D39B7D6A-118E-49A0-BE97-86074BAE05AD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA656F71-65D8-427F-95DB-0F828384A833}"/>
 </file>
--- a/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
+++ b/____EvoM1_TraitTable/corticospinaltract_etc.xlsx
@@ -1572,13 +1572,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05B840FD-5718-4EFE-BE82-D414873726FE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFD106C4-7107-4436-8ABD-B47F6CDD2DB7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58004295-57F5-43BD-9954-C99ADE0D3549}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7529F92-5A01-4285-A306-F999AE206C52}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA656F71-65D8-427F-95DB-0F828384A833}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B85948E2-E314-4DE8-BF1D-15145C7317D4}"/>
 </file>